--- a/Codebook.xlsx
+++ b/Codebook.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/home/Downloads/AIQuality-Replication-Package-master/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/home/Desktop/AIModelQuality/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFDC946A-1BCA-8D4D-BD5D-D6F9649ED3F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2960BECA-538A-D14C-B04F-92DE5BBFE67E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4240" yWindow="620" windowWidth="57040" windowHeight="25300" activeTab="1" xr2:uid="{CD8DBCD4-70E6-6841-82EA-79066243C39A}"/>
+    <workbookView xWindow="7340" yWindow="-21000" windowWidth="26480" windowHeight="21000" activeTab="1" xr2:uid="{CD8DBCD4-70E6-6841-82EA-79066243C39A}"/>
   </bookViews>
   <sheets>
-    <sheet name="Closed Coding" sheetId="1" r:id="rId1"/>
-    <sheet name="Axial Coding" sheetId="2" r:id="rId2"/>
+    <sheet name="1" sheetId="1" r:id="rId1"/>
+    <sheet name="2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="75">
   <si>
     <t>Definition</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -136,16 +136,10 @@
   </si>
   <si>
     <t>Challenge</t>
-  </si>
-  <si>
-    <t>Challenge</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Solution</t>
-  </si>
-  <si>
-    <t>Solution</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -181,18 +175,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Perception driven by compliance requirement.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>RealTimeTradeoff</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Importance tradeoff between correctness and efficiency for real-time applications.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>MicroserviceReliefScalDeploy</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -201,30 +187,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Scenario where explianability is still a top concern even without compliance need, aiming at human-centric decision making.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RobustnessImbalance</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AI robustness becomes critical when the deployment environment exhibits either rapid data drift or pronounced class imbalance.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>The usage of microservice arch which relief the scalability and deployability burden.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Related RQ Code</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>ImbalancedData</t>
-  </si>
-  <si>
-    <t>ImbalancedData</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -232,17 +199,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>OfflineOnlineMisalign</t>
-  </si>
-  <si>
-    <t>OfflineOnlineMisalign</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Improvements in offline metrics (e.g., accuracy) often fail to produce gains in online, real-world business value.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>DataDrift</t>
   </si>
   <si>
@@ -276,109 +232,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>EnvHeterogeneity</t>
-  </si>
-  <si>
-    <t>EnvHeterogeneity</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Diverse hardware and software environments create compatibility issues during deployment.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>OutputCompliance</t>
-  </si>
-  <si>
-    <t>OutputCompliance</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Generative models may produce outputs violating laws and regulations.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ExplainabilityMethodChoice</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Different explainability methods have distinct trade-offs, making selection challenging.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>WorkloadSpike</t>
-  </si>
-  <si>
-    <t>Unexpected workload surges can cause performance degradation or even crash.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TrainingDataBreach</t>
-  </si>
-  <si>
-    <t>TrainingDataBreach</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>The risk of leaking sensitive and confidential data used for training via direct and indirect exposure.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DemographicDataBias</t>
-  </si>
-  <si>
-    <t>DemographicDataBias</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Collected data often fails to accurately represent real-world demographic distributions.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ActiveLearning</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Active Learning.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DataResampling</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Data Resampling.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DataAugmentation</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Data Augmentation.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RuleSystem</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Rule-based expert system.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Rapid canary release.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CanaryRelease</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Frequent model updates based on three triggers.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ModelUpdate</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -399,102 +256,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Efficient model pipeline.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>EffModelPipeline</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>AIAnno</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Platform-aligned model optimization.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ModelOpt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Model serving platforms.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>AI-assisted data annotation.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ModelServing</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Reinforcement learning from human feedback (RLHF) combined with rule-based keyword filtering</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RLHFFilter</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I/O guardrails</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>IOGuard</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cloud computing and container orchestration.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CloudContainer</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>InHouseDev</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>In-house model training and deployment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sensitive data classification</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DataClassification</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DataAnonymize</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Data anonymization</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stratified sampling</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>StratifiedSampling</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DataResampAugBias</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Data resampling and data augmentation for bias mitigation.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>For theme related to solution, here it shows the corresponding challenge theme.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -512,6 +281,49 @@
   </si>
   <si>
     <t>Related Quality Attribute Code 4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>·</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Maintainability</t>
+  </si>
+  <si>
+    <t>It refers to the ease with which an AI model can be updated, debugged, and improved over time. We focus on operational concerns like model upgrading and monitoring in this study.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DataResamplingAugmentation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>While previously considered challenging, deployability and scalability are now handled by microservices. AI teams containerize models and expose APIs for seamless integration, and utilize platform infrastructure for dynamic scaling.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Compliance translates legal mandates into quality attributes: safety necessitates robustness in GenAI, auditability requires explainability in finance, anti-discrimination dictates fairness for demographics, and data protection enforces privacy.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>In real-time AI, operational cost, response latency, and model capability form a three-way tradeoff. Practitioners prioritize efficiency by optimizing latency and cost, while ensuring correctness remains within acceptable limits.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Beyond compliance, explainability aids maintainability and fosters user trust. While industry practitioners used to focus primarily on the former, today they place equal importance on the latter.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Active learning.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Data resampling and augmentation.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pragmatic retraining based on time or newly collected data volume</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -584,10 +396,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -923,27 +735,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63B45E73-14A7-9345-8341-413894359430}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="37.33203125" customWidth="1"/>
-    <col min="3" max="3" width="144.5" customWidth="1"/>
+    <col min="3" max="3" width="163.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="5" t="s">
-        <v>32</v>
+      <c r="A2" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>2</v>
@@ -953,7 +765,7 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="5"/>
+      <c r="A3" s="4"/>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
@@ -962,7 +774,7 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="5"/>
+      <c r="A4" s="4"/>
       <c r="B4" s="2" t="s">
         <v>8</v>
       </c>
@@ -971,7 +783,7 @@
       </c>
     </row>
     <row r="5" spans="1:3" ht="17">
-      <c r="A5" s="5"/>
+      <c r="A5" s="4"/>
       <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
@@ -980,7 +792,7 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="5"/>
+      <c r="A6" s="4"/>
       <c r="B6" s="2" t="s">
         <v>14</v>
       </c>
@@ -989,7 +801,7 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="5"/>
+      <c r="A7" s="4"/>
       <c r="B7" s="2" t="s">
         <v>17</v>
       </c>
@@ -998,7 +810,7 @@
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="5"/>
+      <c r="A8" s="4"/>
       <c r="B8" s="2" t="s">
         <v>20</v>
       </c>
@@ -1007,7 +819,7 @@
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="5"/>
+      <c r="A9" s="4"/>
       <c r="B9" s="2" t="s">
         <v>22</v>
       </c>
@@ -1016,38 +828,52 @@
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="3" t="s">
+      <c r="A10" s="4"/>
+      <c r="B10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C11" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="4"/>
-      <c r="B11" s="3" t="s">
+    <row r="12" spans="1:3">
+      <c r="A12" s="5"/>
+      <c r="B12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="5"/>
+      <c r="B13" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="4"/>
-      <c r="B12" s="3" t="s">
+      <c r="C13" t="s">
         <v>29</v>
       </c>
-      <c r="C12" t="s">
-        <v>31</v>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:A9"/>
-    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A2:A10"/>
+    <mergeCell ref="A11:A13"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1060,54 +886,54 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66AD20E8-5907-0F4C-B7B1-2541A111F7BB}">
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="30.1640625" customWidth="1"/>
-    <col min="2" max="2" width="96.5" customWidth="1"/>
+    <col min="2" max="2" width="123.5" style="1" customWidth="1"/>
     <col min="3" max="3" width="16.33203125" customWidth="1"/>
     <col min="4" max="7" width="30.33203125" customWidth="1"/>
     <col min="8" max="8" width="72.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" ht="17">
       <c r="A1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D1" t="s">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="E1" t="s">
-        <v>121</v>
+        <v>61</v>
       </c>
       <c r="F1" t="s">
-        <v>122</v>
+        <v>62</v>
       </c>
       <c r="G1" t="s">
-        <v>123</v>
+        <v>63</v>
       </c>
       <c r="H1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="34">
       <c r="A2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" t="s">
         <v>13</v>
@@ -1119,14 +945,14 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="17">
+    <row r="3" spans="1:8" ht="34">
       <c r="A3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" s="4"/>
+        <v>36</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" s="5"/>
       <c r="D3" t="s">
         <v>1</v>
       </c>
@@ -1134,14 +960,14 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="17">
+    <row r="4" spans="1:8" ht="34">
       <c r="A4" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C4" s="4"/>
+        <v>37</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="5"/>
       <c r="D4" t="s">
         <v>19</v>
       </c>
@@ -1149,40 +975,52 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="17">
+    <row r="5" spans="1:8" ht="34">
       <c r="A5" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C5" s="4"/>
+        <v>38</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="5"/>
       <c r="D5" t="s">
         <v>13</v>
       </c>
+      <c r="E5" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="6" spans="1:8" ht="17">
       <c r="A6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" s="4"/>
+        <v>40</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="D6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
         <v>4</v>
+      </c>
+      <c r="F6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="17">
       <c r="A7" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>26</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="5"/>
       <c r="D7" t="s">
         <v>1</v>
       </c>
@@ -1190,520 +1028,175 @@
         <v>4</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="17">
       <c r="A8" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" s="4"/>
+        <v>46</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="5"/>
       <c r="D8" t="s">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="17">
       <c r="A9" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B9" t="s">
-        <v>56</v>
-      </c>
-      <c r="C9" s="4"/>
+        <v>49</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="5"/>
       <c r="D9" t="s">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="F9" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="17">
       <c r="A10" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B10" t="s">
-        <v>59</v>
-      </c>
-      <c r="C10" s="4"/>
+        <v>51</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="D10" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>13</v>
+      </c>
+      <c r="F10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="17">
       <c r="A11" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B11" t="s">
-        <v>62</v>
-      </c>
-      <c r="C11" s="4"/>
+        <v>67</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="5"/>
       <c r="D11" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>13</v>
+      </c>
+      <c r="F11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="17">
       <c r="A12" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" s="5"/>
+      <c r="D12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" t="s">
         <v>65</v>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" t="s">
-        <v>22</v>
+      <c r="H12" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="17">
-      <c r="A13" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B13" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13" s="4"/>
+      <c r="A13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="5"/>
       <c r="D13" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>7</v>
+      </c>
+      <c r="H13" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="17">
       <c r="A14" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" s="4"/>
+        <v>55</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="5"/>
       <c r="D14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" t="s">
-        <v>71</v>
-      </c>
-      <c r="B15" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="E14" t="s">
+        <v>7</v>
+      </c>
+      <c r="H14" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="17">
+      <c r="A15" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="5"/>
       <c r="D15" t="s">
+        <v>1</v>
+      </c>
+      <c r="E15" t="s">
         <v>7</v>
       </c>
-      <c r="E15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="17">
-      <c r="A16" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B16" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16" s="4"/>
-      <c r="D16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="17">
-      <c r="A17" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B17" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" s="4"/>
-      <c r="D17" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="17">
-      <c r="A18" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B18" t="s">
-        <v>80</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D18" t="s">
-        <v>4</v>
-      </c>
-      <c r="E18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18" t="s">
-        <v>16</v>
-      </c>
-      <c r="H18" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="17">
-      <c r="A19" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19" s="4"/>
-      <c r="D19" t="s">
-        <v>4</v>
-      </c>
-      <c r="E19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19" t="s">
-        <v>16</v>
-      </c>
-      <c r="H19" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="17">
-      <c r="A20" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B20" t="s">
-        <v>84</v>
-      </c>
-      <c r="C20" s="4"/>
-      <c r="D20" t="s">
-        <v>4</v>
-      </c>
-      <c r="E20" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" t="s">
-        <v>10</v>
-      </c>
-      <c r="G20" t="s">
-        <v>16</v>
-      </c>
-      <c r="H20" t="s">
+      <c r="F15" t="s">
+        <v>65</v>
+      </c>
+      <c r="H15" t="s">
         <v>48</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="17">
-      <c r="A21" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B21" t="s">
-        <v>86</v>
-      </c>
-      <c r="C21" s="4"/>
-      <c r="D21" t="s">
-        <v>4</v>
-      </c>
-      <c r="E21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F21" t="s">
-        <v>10</v>
-      </c>
-      <c r="G21" t="s">
-        <v>16</v>
-      </c>
-      <c r="H21" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="17">
-      <c r="A22" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B22" t="s">
-        <v>87</v>
-      </c>
-      <c r="C22" s="4"/>
-      <c r="D22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E22" t="s">
-        <v>4</v>
-      </c>
-      <c r="H22" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="17">
-      <c r="A23" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B23" t="s">
-        <v>89</v>
-      </c>
-      <c r="C23" s="4"/>
-      <c r="D23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E23" t="s">
-        <v>4</v>
-      </c>
-      <c r="H23" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" t="s">
-        <v>91</v>
-      </c>
-      <c r="B24" t="s">
-        <v>92</v>
-      </c>
-      <c r="C24" s="4"/>
-      <c r="D24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="H24" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="17">
-      <c r="A25" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B25" t="s">
-        <v>94</v>
-      </c>
-      <c r="C25" s="4"/>
-      <c r="D25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E25" t="s">
-        <v>7</v>
-      </c>
-      <c r="H25" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="17">
-      <c r="A26" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B26" t="s">
-        <v>95</v>
-      </c>
-      <c r="C26" s="4"/>
-      <c r="D26" t="s">
-        <v>1</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="H26" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="17">
-      <c r="A27" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B27" t="s">
-        <v>101</v>
-      </c>
-      <c r="C27" s="4"/>
-      <c r="D27" t="s">
-        <v>1</v>
-      </c>
-      <c r="E27" t="s">
-        <v>7</v>
-      </c>
-      <c r="H27" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="17">
-      <c r="A28" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B28" t="s">
-        <v>98</v>
-      </c>
-      <c r="C28" s="4"/>
-      <c r="D28" t="s">
-        <v>22</v>
-      </c>
-      <c r="H28" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="17">
-      <c r="A29" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B29" t="s">
-        <v>100</v>
-      </c>
-      <c r="C29" s="4"/>
-      <c r="D29" t="s">
-        <v>22</v>
-      </c>
-      <c r="H29" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="17">
-      <c r="A30" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B30" t="s">
-        <v>103</v>
-      </c>
-      <c r="C30" s="4"/>
-      <c r="D30" t="s">
-        <v>4</v>
-      </c>
-      <c r="E30" t="s">
-        <v>10</v>
-      </c>
-      <c r="H30" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="17">
-      <c r="A31" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B31" t="s">
-        <v>105</v>
-      </c>
-      <c r="C31" s="4"/>
-      <c r="D31" t="s">
-        <v>4</v>
-      </c>
-      <c r="E31" t="s">
-        <v>10</v>
-      </c>
-      <c r="H31" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="17">
-      <c r="A32" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B32" t="s">
-        <v>107</v>
-      </c>
-      <c r="C32" s="4"/>
-      <c r="D32" t="s">
-        <v>7</v>
-      </c>
-      <c r="E32" t="s">
-        <v>19</v>
-      </c>
-      <c r="H32" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="17">
-      <c r="A33" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B33" t="s">
-        <v>110</v>
-      </c>
-      <c r="C33" s="4"/>
-      <c r="D33" t="s">
-        <v>16</v>
-      </c>
-      <c r="H33" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="17">
-      <c r="A34" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B34" t="s">
-        <v>111</v>
-      </c>
-      <c r="C34" s="4"/>
-      <c r="D34" t="s">
-        <v>16</v>
-      </c>
-      <c r="H34" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="17">
-      <c r="A35" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B35" t="s">
-        <v>114</v>
-      </c>
-      <c r="C35" s="4"/>
-      <c r="D35" t="s">
-        <v>16</v>
-      </c>
-      <c r="H35" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="17">
-      <c r="A36" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B36" t="s">
-        <v>115</v>
-      </c>
-      <c r="C36" s="4"/>
-      <c r="D36" t="s">
-        <v>10</v>
-      </c>
-      <c r="H36" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="17">
-      <c r="A37" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B37" t="s">
-        <v>118</v>
-      </c>
-      <c r="C37" s="4"/>
-      <c r="D37" t="s">
-        <v>10</v>
-      </c>
-      <c r="H37" t="s">
-        <v>76</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="C2:C6"/>
-    <mergeCell ref="C7:C17"/>
-    <mergeCell ref="C18:C37"/>
+    <mergeCell ref="C2:C5"/>
+    <mergeCell ref="C6:C9"/>
+    <mergeCell ref="C10:C15"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1713,15 +1206,15 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8EB1C31B-CB36-F74A-9707-56C56393DBF6}">
           <x14:formula1>
-            <xm:f>'Closed Coding'!$B$10:$B$12</xm:f>
+            <xm:f>'1'!$B$11:$B$13</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C37</xm:sqref>
+          <xm:sqref>C2:C15</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0FAC3345-03EB-004F-89C8-C368CB11974F}">
           <x14:formula1>
-            <xm:f>'Closed Coding'!$B$2:$B$9</xm:f>
+            <xm:f>'1'!$B$2:$B$10</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:G37</xm:sqref>
+          <xm:sqref>D2:G15</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
